--- a/outputs/generated/nitro_bioisostere_campaign/mol2mol_similarity/plain/mol2mol_similarity_plain_generated_optimal.xlsx
+++ b/outputs/generated/nitro_bioisostere_campaign/mol2mol_similarity/plain/mol2mol_similarity_plain_generated_optimal.xlsx
@@ -614,23 +614,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:BF7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="4" width="14.7109375" customWidth="1"/>
     <col min="5" max="6" width="12.7109375" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" customWidth="1"/>
-    <col min="9" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="16.7109375" customWidth="1"/>
-    <col min="12" max="12" width="32.7109375" customWidth="1"/>
-    <col min="13" max="13" width="28.7109375" customWidth="1"/>
-    <col min="14" max="14" width="37.7109375" customWidth="1"/>
-    <col min="15" max="15" width="38.7109375" customWidth="1"/>
-    <col min="16" max="16" width="30.7109375" customWidth="1"/>
-    <col min="17" max="17" width="16.7109375" customWidth="1"/>
+    <col min="7" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="31.7109375" customWidth="1"/>
+    <col min="13" max="13" width="30.7109375" customWidth="1"/>
+    <col min="14" max="14" width="28.7109375" customWidth="1"/>
+    <col min="15" max="15" width="27.7109375" customWidth="1"/>
+    <col min="16" max="16" width="26.7109375" customWidth="1"/>
+    <col min="17" max="17" width="25.7109375" customWidth="1"/>
+    <col min="18" max="19" width="22.7109375" customWidth="1"/>
+    <col min="20" max="21" width="20.7109375" customWidth="1"/>
+    <col min="22" max="22" width="24.7109375" customWidth="1"/>
+    <col min="23" max="23" width="12.7109375" customWidth="1"/>
+    <col min="24" max="24" width="16.7109375" customWidth="1"/>
+    <col min="25" max="25" width="32.7109375" customWidth="1"/>
+    <col min="26" max="26" width="28.7109375" customWidth="1"/>
+    <col min="27" max="27" width="37.7109375" customWidth="1"/>
+    <col min="28" max="28" width="38.7109375" customWidth="1"/>
+    <col min="29" max="29" width="30.7109375" customWidth="1"/>
+    <col min="30" max="31" width="13.7109375" customWidth="1"/>
+    <col min="32" max="35" width="12.7109375" customWidth="1"/>
+    <col min="36" max="36" width="21.7109375" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" customWidth="1"/>
+    <col min="39" max="39" width="15.7109375" customWidth="1"/>
+    <col min="40" max="42" width="14.7109375" customWidth="1"/>
+    <col min="43" max="43" width="12.7109375" customWidth="1"/>
+    <col min="44" max="44" width="20.7109375" customWidth="1"/>
+    <col min="45" max="45" width="13.7109375" customWidth="1"/>
+    <col min="46" max="46" width="17.7109375" customWidth="1"/>
+    <col min="47" max="48" width="12.7109375" customWidth="1"/>
+    <col min="49" max="49" width="15.7109375" customWidth="1"/>
+    <col min="50" max="50" width="18.7109375" customWidth="1"/>
+    <col min="51" max="54" width="12.7109375" customWidth="1"/>
+    <col min="55" max="55" width="18.7109375" customWidth="1"/>
+    <col min="56" max="56" width="23.7109375" customWidth="1"/>
+    <col min="57" max="57" width="25.7109375" customWidth="1"/>
+    <col min="58" max="58" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -666,55 +695,260 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>qsar_model_count</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>qsar_models_used</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>pred_logIC50_uM</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>pred_ic50_uM</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>pred_pIC50</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>pred_logIC50_uM_ensemble_mean</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pred_logIC50_uM_ensemble_std</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>pred_ic50_uM_ensemble_mean</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>pred_ic50_uM_ensemble_std</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>pred_pIC50_ensemble_mean</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>pred_pIC50_ensemble_std</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>pred_ic50_uM_lower95</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>pred_ic50_uM_upper95</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>pred_pIC50_lower95</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>pred_pIC50_upper95</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>pred_pIC50_uncertainty</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>pred_cLogP</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pred_logS_ESOL</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>pred_Solubility_ESOL_mol_per_L</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pred_Solubility_ESOL_class</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>pred_MetStab_Clearance_Microsome_AZ</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pred_MetStab_Clearance_Hepatocyte_AZ</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>pred_MetStab_Half_Life_Obach</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>PAINS_alert</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>BRENK_alert</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>NIH_alert</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>AMES</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ClinTox</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>DILI</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Carcinogens_Lagunin</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>hERG</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>CYP1A2_Veith</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>CYP2C19_Veith</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>CYP2C9_Veith</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>CYP2D6_Veith</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>CYP3A4_Veith</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>HIA_Hou</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Bioavailability_Ma</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>PAMPA_NCATS</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>Pgp_Broccatelli</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Caco2_Wang</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>PPBR_AZ</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>VDss_Lombardo</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>molecular_weight</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>logP</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>QED</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>Lipinski</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>sa_score</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>sa_accessibility</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>liability_alert_count</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>passes_qsar_uncertainty</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>passes_optimal</t>
         </is>
@@ -723,7 +957,7 @@
     <row r="2" ht="92" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CC(C)(C)OC(=O)N1CC2(CCN(c3cncc(C#CC4CC4)c3)C2)C1</t>
+          <t>CC(C)(C)OC(=O)N1CCC2(C1)CN(c1cncc(C#CC3CC3)c1)C2</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -735,51 +969,176 @@
         <v>1</v>
       </c>
       <c r="E2" s="3">
-        <v>0.3779527559055118</v>
+        <v>0.3565891472868217</v>
       </c>
       <c r="F2" s="3">
-        <v>7.29</v>
+        <v>9.82</v>
       </c>
       <c r="G2" s="3">
-        <v>0.6051538950805846</v>
-      </c>
-      <c r="H2" s="3">
-        <v>4.028597650189411</v>
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I2" s="3">
-        <v>5.394846104919416</v>
+        <v>0.6051538968907209</v>
       </c>
       <c r="J2" s="3">
+        <v>4.028597666980577</v>
+      </c>
+      <c r="K2" s="3">
+        <v>5.394846103109279</v>
+      </c>
+      <c r="L2" s="3">
+        <v>0.8824989854002624</v>
+      </c>
+      <c r="M2" s="3">
+        <v>0.3228250251742513</v>
+      </c>
+      <c r="N2" s="3">
+        <v>10.34297534030582</v>
+      </c>
+      <c r="O2" s="3">
+        <v>8.855951904205119</v>
+      </c>
+      <c r="P2" s="3">
+        <v>5.117501014599737</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>0.3228250251742513</v>
+      </c>
+      <c r="R2" s="3">
+        <v>1.777304891104969</v>
+      </c>
+      <c r="S2" s="3">
+        <v>32.75186496525397</v>
+      </c>
+      <c r="T2" s="3">
+        <v>4.484763965258205</v>
+      </c>
+      <c r="U2" s="3">
+        <v>5.75023806394127</v>
+      </c>
+      <c r="V2" s="3">
+        <v>0.3228250251742513</v>
+      </c>
+      <c r="W2" s="3">
         <v>3.290300000000002</v>
       </c>
-      <c r="K2" s="3">
+      <c r="X2" s="3">
         <v>-4.6118160103259</v>
       </c>
-      <c r="L2" s="3">
+      <c r="Y2" s="3">
         <v>2.444465935948885E-05</v>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N2" s="3">
-        <v>60.52811431884766</v>
-      </c>
-      <c r="O2" s="3">
-        <v>54.04392242431641</v>
-      </c>
-      <c r="P2" s="3">
-        <v>41.54251098632812</v>
-      </c>
-      <c r="Q2" s="3">
+      <c r="AA2" s="3">
+        <v>56.56463623046875</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>51.99232864379883</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>40.70726776123047</v>
+      </c>
+      <c r="AD2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="3">
+        <v>0.177259087562561</v>
+      </c>
+      <c r="AH2" s="3">
+        <v>0.2245453596115112</v>
+      </c>
+      <c r="AI2" s="3">
+        <v>0.692952036857605</v>
+      </c>
+      <c r="AJ2" s="3">
+        <v>0.0883786603808403</v>
+      </c>
+      <c r="AK2" s="3">
+        <v>0.6438459157943726</v>
+      </c>
+      <c r="AL2" s="3">
+        <v>0.2338467091321945</v>
+      </c>
+      <c r="AM2" s="3">
+        <v>0.5687931776046753</v>
+      </c>
+      <c r="AN2" s="3">
+        <v>0.5209888219833374</v>
+      </c>
+      <c r="AO2" s="3">
+        <v>0.08753232657909393</v>
+      </c>
+      <c r="AP2" s="3">
+        <v>0.7143261432647705</v>
+      </c>
+      <c r="AQ2" s="3">
+        <v>0.9997826814651489</v>
+      </c>
+      <c r="AR2" s="3">
+        <v>0.7694124579429626</v>
+      </c>
+      <c r="AS2" s="3">
+        <v>0.9653592109680176</v>
+      </c>
+      <c r="AT2" s="3">
+        <v>0.5967809557914734</v>
+      </c>
+      <c r="AU2" s="3">
+        <v>-4.551844596862793</v>
+      </c>
+      <c r="AV2" s="3">
+        <v>94.36016845703125</v>
+      </c>
+      <c r="AW2" s="3">
+        <v>8.904187202453613</v>
+      </c>
+      <c r="AX2" s="3">
+        <v>353.4660000000002</v>
+      </c>
+      <c r="AY2" s="3">
+        <v>3.290300000000002</v>
+      </c>
+      <c r="AZ2" s="3">
+        <v>0.7270065061949308</v>
+      </c>
+      <c r="BA2" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB2" s="3">
+        <v>3.444288329613787</v>
+      </c>
+      <c r="BC2" s="3">
+        <v>0.7284124078206904</v>
+      </c>
+      <c r="BD2" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE2" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF2" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="92" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CC(C)(C)OC(=O)N1CCC2(C1)CN(c1cncc(C#CC3CC3)c1)C2</t>
+          <t>CC(C)(C)OC(=O)N1CC2(CCN(c3cncc(C#CC4CC4)c3)C2)C1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -791,44 +1150,169 @@
         <v>1</v>
       </c>
       <c r="E3" s="3">
-        <v>0.3565891472868217</v>
+        <v>0.3779527559055118</v>
       </c>
       <c r="F3" s="3">
-        <v>9.82</v>
+        <v>7.29</v>
       </c>
       <c r="G3" s="3">
-        <v>0.6051538950805846</v>
-      </c>
-      <c r="H3" s="3">
-        <v>4.028597650189411</v>
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I3" s="3">
-        <v>5.394846104919416</v>
+        <v>0.6051538968907209</v>
       </c>
       <c r="J3" s="3">
+        <v>4.028597666980577</v>
+      </c>
+      <c r="K3" s="3">
+        <v>5.394846103109279</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0.8957491087190782</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0.3281876103103729</v>
+      </c>
+      <c r="N3" s="3">
+        <v>10.6493487168374</v>
+      </c>
+      <c r="O3" s="3">
+        <v>8.772131703379241</v>
+      </c>
+      <c r="P3" s="3">
+        <v>5.104250891280921</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>0.3281876103103729</v>
+      </c>
+      <c r="R3" s="3">
+        <v>1.788551263863722</v>
+      </c>
+      <c r="S3" s="3">
+        <v>34.59368487158814</v>
+      </c>
+      <c r="T3" s="3">
+        <v>4.461003175072591</v>
+      </c>
+      <c r="U3" s="3">
+        <v>5.747498607489253</v>
+      </c>
+      <c r="V3" s="3">
+        <v>0.3281876103103729</v>
+      </c>
+      <c r="W3" s="3">
         <v>3.290300000000002</v>
       </c>
-      <c r="K3" s="3">
+      <c r="X3" s="3">
         <v>-4.6118160103259</v>
       </c>
-      <c r="L3" s="3">
+      <c r="Y3" s="3">
         <v>2.444465935948885E-05</v>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N3" s="3">
-        <v>56.56463623046875</v>
-      </c>
-      <c r="O3" s="3">
-        <v>51.99232864379883</v>
-      </c>
-      <c r="P3" s="3">
-        <v>40.70726776123047</v>
-      </c>
-      <c r="Q3" s="3">
+      <c r="AA3" s="3">
+        <v>60.52811431884766</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>54.04392242431641</v>
+      </c>
+      <c r="AC3" s="3">
+        <v>41.54251098632812</v>
+      </c>
+      <c r="AD3" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="3">
+        <v>0.1817121505737305</v>
+      </c>
+      <c r="AH3" s="3">
+        <v>0.2259128093719482</v>
+      </c>
+      <c r="AI3" s="3">
+        <v>0.6951167583465576</v>
+      </c>
+      <c r="AJ3" s="3">
+        <v>0.09010275453329086</v>
+      </c>
+      <c r="AK3" s="3">
+        <v>0.6656471490859985</v>
+      </c>
+      <c r="AL3" s="3">
+        <v>0.2871345579624176</v>
+      </c>
+      <c r="AM3" s="3">
+        <v>0.5867720246315002</v>
+      </c>
+      <c r="AN3" s="3">
+        <v>0.5658631920814514</v>
+      </c>
+      <c r="AO3" s="3">
+        <v>0.09989241510629654</v>
+      </c>
+      <c r="AP3" s="3">
+        <v>0.7679430246353149</v>
+      </c>
+      <c r="AQ3" s="3">
+        <v>0.9997621774673462</v>
+      </c>
+      <c r="AR3" s="3">
+        <v>0.7646519541740417</v>
+      </c>
+      <c r="AS3" s="3">
+        <v>0.967028021812439</v>
+      </c>
+      <c r="AT3" s="3">
+        <v>0.6451165676116943</v>
+      </c>
+      <c r="AU3" s="3">
+        <v>-4.58236026763916</v>
+      </c>
+      <c r="AV3" s="3">
+        <v>95.09494018554688</v>
+      </c>
+      <c r="AW3" s="3">
+        <v>8.92332649230957</v>
+      </c>
+      <c r="AX3" s="3">
+        <v>353.4660000000002</v>
+      </c>
+      <c r="AY3" s="3">
+        <v>3.290300000000002</v>
+      </c>
+      <c r="AZ3" s="3">
+        <v>0.7270065061949308</v>
+      </c>
+      <c r="BA3" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB3" s="3">
+        <v>3.459755637306095</v>
+      </c>
+      <c r="BC3" s="3">
+        <v>0.7266938180771005</v>
+      </c>
+      <c r="BD3" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE3" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF3" s="3">
         <v>1</v>
       </c>
     </row>
@@ -853,38 +1337,163 @@
         <v>9.77</v>
       </c>
       <c r="G4" s="3">
-        <v>0.6051538950805847</v>
-      </c>
-      <c r="H4" s="3">
-        <v>4.028597650189412</v>
+        <v>5</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I4" s="3">
-        <v>5.394846104919416</v>
+        <v>0.6051538968907209</v>
       </c>
       <c r="J4" s="3">
+        <v>4.028597666980577</v>
+      </c>
+      <c r="K4" s="3">
+        <v>5.394846103109279</v>
+      </c>
+      <c r="L4" s="3">
+        <v>1.071027324227294</v>
+      </c>
+      <c r="M4" s="3">
+        <v>0.453485570103045</v>
+      </c>
+      <c r="N4" s="3">
+        <v>17.84268628492911</v>
+      </c>
+      <c r="O4" s="3">
+        <v>11.89399715379812</v>
+      </c>
+      <c r="P4" s="3">
+        <v>4.928972675772706</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>0.453485570103045</v>
+      </c>
+      <c r="R4" s="3">
+        <v>1.521232540661306</v>
+      </c>
+      <c r="S4" s="3">
+        <v>91.17148772678067</v>
+      </c>
+      <c r="T4" s="3">
+        <v>4.040140958370738</v>
+      </c>
+      <c r="U4" s="3">
+        <v>5.817804393174674</v>
+      </c>
+      <c r="V4" s="3">
+        <v>0.453485570103045</v>
+      </c>
+      <c r="W4" s="3">
         <v>2.681100000000002</v>
       </c>
-      <c r="K4" s="3">
+      <c r="X4" s="3">
         <v>-4.469416891183609</v>
       </c>
-      <c r="L4" s="3">
+      <c r="Y4" s="3">
         <v>3.39299413402709E-05</v>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N4" s="3">
+      <c r="AA4" s="3">
         <v>16.76943588256836</v>
       </c>
-      <c r="O4" s="3">
+      <c r="AB4" s="3">
         <v>33.80720520019531</v>
       </c>
-      <c r="P4" s="3">
+      <c r="AC4" s="3">
         <v>41.89714431762695</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="AD4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="3">
+        <v>0.2616260647773743</v>
+      </c>
+      <c r="AH4" s="3">
+        <v>0.2681745886802673</v>
+      </c>
+      <c r="AI4" s="3">
+        <v>0.7960621118545532</v>
+      </c>
+      <c r="AJ4" s="3">
+        <v>0.07101662456989288</v>
+      </c>
+      <c r="AK4" s="3">
+        <v>0.6336730718612671</v>
+      </c>
+      <c r="AL4" s="3">
+        <v>0.07451099902391434</v>
+      </c>
+      <c r="AM4" s="3">
+        <v>0.2241442948579788</v>
+      </c>
+      <c r="AN4" s="3">
+        <v>0.2897434830665588</v>
+      </c>
+      <c r="AO4" s="3">
+        <v>0.03194588422775269</v>
+      </c>
+      <c r="AP4" s="3">
+        <v>0.6579321026802063</v>
+      </c>
+      <c r="AQ4" s="3">
+        <v>0.9988958239555359</v>
+      </c>
+      <c r="AR4" s="3">
+        <v>0.8549615740776062</v>
+      </c>
+      <c r="AS4" s="3">
+        <v>0.8917741775512695</v>
+      </c>
+      <c r="AT4" s="3">
+        <v>0.5444017648696899</v>
+      </c>
+      <c r="AU4" s="3">
+        <v>-4.591850757598877</v>
+      </c>
+      <c r="AV4" s="3">
+        <v>92.46042633056641</v>
+      </c>
+      <c r="AW4" s="3">
+        <v>9.764013290405273</v>
+      </c>
+      <c r="AX4" s="3">
+        <v>389.4990000000001</v>
+      </c>
+      <c r="AY4" s="3">
+        <v>2.681100000000002</v>
+      </c>
+      <c r="AZ4" s="3">
+        <v>0.8204014514733262</v>
+      </c>
+      <c r="BA4" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB4" s="3">
+        <v>3.349548292628201</v>
+      </c>
+      <c r="BC4" s="3">
+        <v>0.7389390785968666</v>
+      </c>
+      <c r="BD4" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE4" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF4" s="3">
         <v>1</v>
       </c>
     </row>
@@ -909,38 +1518,163 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G5" s="3">
-        <v>0.6269673212607438</v>
-      </c>
-      <c r="H5" s="3">
-        <v>4.236110899890319</v>
+        <v>5</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I5" s="3">
-        <v>5.373032678739256</v>
+        <v>0.6269673230267181</v>
       </c>
       <c r="J5" s="3">
+        <v>4.236110917115642</v>
+      </c>
+      <c r="K5" s="3">
+        <v>5.373032676973282</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0.8742033556651265</v>
+      </c>
+      <c r="M5" s="3">
+        <v>0.3438296648732025</v>
+      </c>
+      <c r="N5" s="3">
+        <v>10.15776370613573</v>
+      </c>
+      <c r="O5" s="3">
+        <v>7.669484797807399</v>
+      </c>
+      <c r="P5" s="3">
+        <v>5.125796644334874</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>0.3438296648732025</v>
+      </c>
+      <c r="R5" s="3">
+        <v>1.585978196598272</v>
+      </c>
+      <c r="S5" s="3">
+        <v>35.32722292124513</v>
+      </c>
+      <c r="T5" s="3">
+        <v>4.451890501183397</v>
+      </c>
+      <c r="U5" s="3">
+        <v>5.799702787486351</v>
+      </c>
+      <c r="V5" s="3">
+        <v>0.3438296648732025</v>
+      </c>
+      <c r="W5" s="3">
         <v>3.316100000000002</v>
       </c>
-      <c r="K5" s="3">
+      <c r="X5" s="3">
         <v>-4.840572534996578</v>
       </c>
-      <c r="L5" s="3">
+      <c r="Y5" s="3">
         <v>1.443535487743144E-05</v>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N5" s="3">
-        <v>60.20294189453125</v>
-      </c>
-      <c r="O5" s="3">
+      <c r="AA5" s="3">
+        <v>60.20293426513672</v>
+      </c>
+      <c r="AB5" s="3">
         <v>61.03471755981445</v>
       </c>
-      <c r="P5" s="3">
-        <v>46.73542404174805</v>
-      </c>
-      <c r="Q5" s="3">
+      <c r="AC5" s="3">
+        <v>46.73542022705078</v>
+      </c>
+      <c r="AD5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="3">
+        <v>0.2031314820051193</v>
+      </c>
+      <c r="AH5" s="3">
+        <v>0.2511689364910126</v>
+      </c>
+      <c r="AI5" s="3">
+        <v>0.8450652360916138</v>
+      </c>
+      <c r="AJ5" s="3">
+        <v>0.1027115136384964</v>
+      </c>
+      <c r="AK5" s="3">
+        <v>0.6776825189590454</v>
+      </c>
+      <c r="AL5" s="3">
+        <v>0.4971807599067688</v>
+      </c>
+      <c r="AM5" s="3">
+        <v>0.5462123155593872</v>
+      </c>
+      <c r="AN5" s="3">
+        <v>0.6626511216163635</v>
+      </c>
+      <c r="AO5" s="3">
+        <v>0.08121009171009064</v>
+      </c>
+      <c r="AP5" s="3">
+        <v>0.8647303581237793</v>
+      </c>
+      <c r="AQ5" s="3">
+        <v>0.9997215270996094</v>
+      </c>
+      <c r="AR5" s="3">
+        <v>0.8227964639663696</v>
+      </c>
+      <c r="AS5" s="3">
+        <v>0.9525008201599121</v>
+      </c>
+      <c r="AT5" s="3">
+        <v>0.6856838464736938</v>
+      </c>
+      <c r="AU5" s="3">
+        <v>-4.631178855895996</v>
+      </c>
+      <c r="AV5" s="3">
+        <v>98.99516296386719</v>
+      </c>
+      <c r="AW5" s="3">
+        <v>5.876406669616699</v>
+      </c>
+      <c r="AX5" s="3">
+        <v>373.4560000000001</v>
+      </c>
+      <c r="AY5" s="3">
+        <v>3.316100000000002</v>
+      </c>
+      <c r="AZ5" s="3">
+        <v>0.6116733295874957</v>
+      </c>
+      <c r="BA5" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB5" s="3">
+        <v>3.29505762412903</v>
+      </c>
+      <c r="BC5" s="3">
+        <v>0.7449935973189967</v>
+      </c>
+      <c r="BD5" s="3">
+        <v>2</v>
+      </c>
+      <c r="BE5" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF5" s="3">
         <v>1</v>
       </c>
     </row>
@@ -965,38 +1699,163 @@
         <v>9.43</v>
       </c>
       <c r="G6" s="3">
-        <v>0.6976196057554537</v>
-      </c>
-      <c r="H6" s="3">
-        <v>4.984477107800574</v>
+        <v>5</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I6" s="3">
-        <v>5.302380394244547</v>
+        <v>0.6976196075069574</v>
       </c>
       <c r="J6" s="3">
+        <v>4.984477127902903</v>
+      </c>
+      <c r="K6" s="3">
+        <v>5.302380392493043</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0.8953558571396633</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0.1873493021644952</v>
+      </c>
+      <c r="N6" s="3">
+        <v>8.599463762035141</v>
+      </c>
+      <c r="O6" s="3">
+        <v>3.534988500955275</v>
+      </c>
+      <c r="P6" s="3">
+        <v>5.104644142860336</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>0.1873493021644952</v>
+      </c>
+      <c r="R6" s="3">
+        <v>3.3740477531375</v>
+      </c>
+      <c r="S6" s="3">
+        <v>18.30461038738765</v>
+      </c>
+      <c r="T6" s="3">
+        <v>4.737439510617926</v>
+      </c>
+      <c r="U6" s="3">
+        <v>5.471848775102748</v>
+      </c>
+      <c r="V6" s="3">
+        <v>0.1873493021644952</v>
+      </c>
+      <c r="W6" s="3">
         <v>3.478700000000003</v>
       </c>
-      <c r="K6" s="3">
+      <c r="X6" s="3">
         <v>-5.005884394500141</v>
       </c>
-      <c r="L6" s="3">
+      <c r="Y6" s="3">
         <v>9.865420597934993E-06</v>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N6" s="3">
+      <c r="AA6" s="3">
         <v>45.21793365478516</v>
       </c>
-      <c r="O6" s="3">
-        <v>49.32835006713867</v>
-      </c>
-      <c r="P6" s="3">
+      <c r="AB6" s="3">
+        <v>49.32834625244141</v>
+      </c>
+      <c r="AC6" s="3">
         <v>40.18856048583984</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="AD6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3">
+        <v>2</v>
+      </c>
+      <c r="AF6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="3">
+        <v>0.1176017299294472</v>
+      </c>
+      <c r="AH6" s="3">
+        <v>0.2769882082939148</v>
+      </c>
+      <c r="AI6" s="3">
+        <v>0.6194230318069458</v>
+      </c>
+      <c r="AJ6" s="3">
+        <v>0.04037143662571907</v>
+      </c>
+      <c r="AK6" s="3">
+        <v>0.6872637867927551</v>
+      </c>
+      <c r="AL6" s="3">
+        <v>0.06891923397779465</v>
+      </c>
+      <c r="AM6" s="3">
+        <v>0.2316244542598724</v>
+      </c>
+      <c r="AN6" s="3">
+        <v>0.24135622382164</v>
+      </c>
+      <c r="AO6" s="3">
+        <v>0.03940944373607635</v>
+      </c>
+      <c r="AP6" s="3">
+        <v>0.7943633794784546</v>
+      </c>
+      <c r="AQ6" s="3">
+        <v>0.9999027252197266</v>
+      </c>
+      <c r="AR6" s="3">
+        <v>0.8274046778678894</v>
+      </c>
+      <c r="AS6" s="3">
+        <v>0.9617129564285278</v>
+      </c>
+      <c r="AT6" s="3">
+        <v>0.5726358294487</v>
+      </c>
+      <c r="AU6" s="3">
+        <v>-4.615780830383301</v>
+      </c>
+      <c r="AV6" s="3">
+        <v>93.75773620605469</v>
+      </c>
+      <c r="AW6" s="3">
+        <v>10.07414436340332</v>
+      </c>
+      <c r="AX6" s="3">
+        <v>395.5470000000003</v>
+      </c>
+      <c r="AY6" s="3">
+        <v>3.478700000000003</v>
+      </c>
+      <c r="AZ6" s="3">
+        <v>0.5656513031600198</v>
+      </c>
+      <c r="BA6" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB6" s="3">
+        <v>3.398238871561463</v>
+      </c>
+      <c r="BC6" s="3">
+        <v>0.7335290142709485</v>
+      </c>
+      <c r="BD6" s="3">
+        <v>2</v>
+      </c>
+      <c r="BE6" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF6" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1021,38 +1880,163 @@
         <v>9.01</v>
       </c>
       <c r="G7" s="3">
-        <v>0.6976196057554538</v>
-      </c>
-      <c r="H7" s="3">
-        <v>4.984477107800576</v>
+        <v>5</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>KNN | KNN | DT | LGBM | ET</t>
+        </is>
       </c>
       <c r="I7" s="3">
-        <v>5.302380394244546</v>
+        <v>0.6976196075069575</v>
       </c>
       <c r="J7" s="3">
+        <v>4.984477127902903</v>
+      </c>
+      <c r="K7" s="3">
+        <v>5.302380392493043</v>
+      </c>
+      <c r="L7" s="3">
+        <v>1.219938036588334</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0.3677264463853309</v>
+      </c>
+      <c r="N7" s="3">
+        <v>22.34409214041806</v>
+      </c>
+      <c r="O7" s="3">
+        <v>14.0908323934721</v>
+      </c>
+      <c r="P7" s="3">
+        <v>4.780061963411666</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0.3677264463853309</v>
+      </c>
+      <c r="R7" s="3">
+        <v>3.156415749265656</v>
+      </c>
+      <c r="S7" s="3">
+        <v>87.23321353587414</v>
+      </c>
+      <c r="T7" s="3">
+        <v>4.059318128496417</v>
+      </c>
+      <c r="U7" s="3">
+        <v>5.500805798326915</v>
+      </c>
+      <c r="V7" s="3">
+        <v>0.3677264463853309</v>
+      </c>
+      <c r="W7" s="3">
         <v>3.080500000000002</v>
       </c>
-      <c r="K7" s="3">
+      <c r="X7" s="3">
         <v>-5.040453903585137</v>
       </c>
-      <c r="L7" s="3">
+      <c r="Y7" s="3">
         <v>9.1105814768203E-06</v>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="Z7" s="2" t="inlineStr">
         <is>
           <t>Moderately Soluble</t>
         </is>
       </c>
-      <c r="N7" s="3">
+      <c r="AA7" s="3">
         <v>31.94557189941406</v>
       </c>
-      <c r="O7" s="3">
+      <c r="AB7" s="3">
         <v>25.61627197265625</v>
       </c>
-      <c r="P7" s="3">
-        <v>50.80401229858398</v>
-      </c>
-      <c r="Q7" s="3">
+      <c r="AC7" s="3">
+        <v>50.80400848388672</v>
+      </c>
+      <c r="AD7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="3">
+        <v>0.1181811913847923</v>
+      </c>
+      <c r="AH7" s="3">
+        <v>0.2883137464523315</v>
+      </c>
+      <c r="AI7" s="3">
+        <v>0.8626953959465027</v>
+      </c>
+      <c r="AJ7" s="3">
+        <v>0.02938465401530266</v>
+      </c>
+      <c r="AK7" s="3">
+        <v>0.7931297421455383</v>
+      </c>
+      <c r="AL7" s="3">
+        <v>0.1443172991275787</v>
+      </c>
+      <c r="AM7" s="3">
+        <v>0.4411754012107849</v>
+      </c>
+      <c r="AN7" s="3">
+        <v>0.6368086934089661</v>
+      </c>
+      <c r="AO7" s="3">
+        <v>0.07752671092748642</v>
+      </c>
+      <c r="AP7" s="3">
+        <v>0.9581480026245117</v>
+      </c>
+      <c r="AQ7" s="3">
+        <v>0.9999772310256958</v>
+      </c>
+      <c r="AR7" s="3">
+        <v>0.7677334547042847</v>
+      </c>
+      <c r="AS7" s="3">
+        <v>0.9165694117546082</v>
+      </c>
+      <c r="AT7" s="3">
+        <v>0.5979740619659424</v>
+      </c>
+      <c r="AU7" s="3">
+        <v>-5.045364856719971</v>
+      </c>
+      <c r="AV7" s="3">
+        <v>96.46507263183594</v>
+      </c>
+      <c r="AW7" s="3">
+        <v>7.68954610824585</v>
+      </c>
+      <c r="AX7" s="3">
+        <v>427.5080000000003</v>
+      </c>
+      <c r="AY7" s="3">
+        <v>3.080500000000002</v>
+      </c>
+      <c r="AZ7" s="3">
+        <v>0.6505517843454918</v>
+      </c>
+      <c r="BA7" s="3">
+        <v>4</v>
+      </c>
+      <c r="BB7" s="3">
+        <v>3.580375515656432</v>
+      </c>
+      <c r="BC7" s="3">
+        <v>0.7132916093715076</v>
+      </c>
+      <c r="BD7" s="3">
+        <v>1</v>
+      </c>
+      <c r="BE7" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF7" s="3">
         <v>1</v>
       </c>
     </row>

--- a/outputs/generated/nitro_bioisostere_campaign/mol2mol_similarity/plain/mol2mol_similarity_plain_generated_optimal.xlsx
+++ b/outputs/generated/nitro_bioisostere_campaign/mol2mol_similarity/plain/mol2mol_similarity_plain_generated_optimal.xlsx
@@ -995,7 +995,7 @@
         <v>0.8824989854002624</v>
       </c>
       <c r="M2" s="3">
-        <v>0.3228250251742513</v>
+        <v>0.3228250251742512</v>
       </c>
       <c r="N2" s="3">
         <v>10.34297534030582</v>
@@ -1007,7 +1007,7 @@
         <v>5.117501014599737</v>
       </c>
       <c r="Q2" s="3">
-        <v>0.3228250251742513</v>
+        <v>0.3228250251742512</v>
       </c>
       <c r="R2" s="3">
         <v>1.777304891104969</v>
@@ -1019,10 +1019,10 @@
         <v>4.484763965258205</v>
       </c>
       <c r="U2" s="3">
-        <v>5.75023806394127</v>
+        <v>5.750238063941271</v>
       </c>
       <c r="V2" s="3">
-        <v>0.3228250251742513</v>
+        <v>0.3228250251742512</v>
       </c>
       <c r="W2" s="3">
         <v>3.290300000000002</v>
@@ -1039,13 +1039,13 @@
         </is>
       </c>
       <c r="AA2" s="3">
-        <v>56.56463623046875</v>
+        <v>56.564636</v>
       </c>
       <c r="AB2" s="3">
-        <v>51.99232864379883</v>
+        <v>51.99233</v>
       </c>
       <c r="AC2" s="3">
-        <v>40.70726776123047</v>
+        <v>40.707268</v>
       </c>
       <c r="AD2" s="3">
         <v>0</v>
@@ -1057,55 +1057,55 @@
         <v>0</v>
       </c>
       <c r="AG2" s="3">
-        <v>0.177259087562561</v>
+        <v>0.17725909</v>
       </c>
       <c r="AH2" s="3">
-        <v>0.2245453596115112</v>
+        <v>0.22454536</v>
       </c>
       <c r="AI2" s="3">
-        <v>0.692952036857605</v>
+        <v>0.69295204</v>
       </c>
       <c r="AJ2" s="3">
-        <v>0.0883786603808403</v>
+        <v>0.08837866</v>
       </c>
       <c r="AK2" s="3">
-        <v>0.6438459157943726</v>
+        <v>0.6438459</v>
       </c>
       <c r="AL2" s="3">
-        <v>0.2338467091321945</v>
+        <v>0.23384671</v>
       </c>
       <c r="AM2" s="3">
-        <v>0.5687931776046753</v>
+        <v>0.5687932</v>
       </c>
       <c r="AN2" s="3">
-        <v>0.5209888219833374</v>
+        <v>0.5209888</v>
       </c>
       <c r="AO2" s="3">
-        <v>0.08753232657909393</v>
+        <v>0.08753233000000001</v>
       </c>
       <c r="AP2" s="3">
-        <v>0.7143261432647705</v>
+        <v>0.7143261400000001</v>
       </c>
       <c r="AQ2" s="3">
-        <v>0.9997826814651489</v>
+        <v>0.9997827</v>
       </c>
       <c r="AR2" s="3">
-        <v>0.7694124579429626</v>
+        <v>0.76941246</v>
       </c>
       <c r="AS2" s="3">
-        <v>0.9653592109680176</v>
+        <v>0.9653592</v>
       </c>
       <c r="AT2" s="3">
-        <v>0.5967809557914734</v>
+        <v>0.59678096</v>
       </c>
       <c r="AU2" s="3">
-        <v>-4.551844596862793</v>
+        <v>-4.5518446</v>
       </c>
       <c r="AV2" s="3">
-        <v>94.36016845703125</v>
+        <v>94.36017</v>
       </c>
       <c r="AW2" s="3">
-        <v>8.904187202453613</v>
+        <v>8.904187</v>
       </c>
       <c r="AX2" s="3">
         <v>353.4660000000002</v>
@@ -1176,7 +1176,7 @@
         <v>0.8957491087190782</v>
       </c>
       <c r="M3" s="3">
-        <v>0.3281876103103729</v>
+        <v>0.3281876103103728</v>
       </c>
       <c r="N3" s="3">
         <v>10.6493487168374</v>
@@ -1188,7 +1188,7 @@
         <v>5.104250891280921</v>
       </c>
       <c r="Q3" s="3">
-        <v>0.3281876103103729</v>
+        <v>0.3281876103103728</v>
       </c>
       <c r="R3" s="3">
         <v>1.788551263863722</v>
@@ -1203,7 +1203,7 @@
         <v>5.747498607489253</v>
       </c>
       <c r="V3" s="3">
-        <v>0.3281876103103729</v>
+        <v>0.3281876103103728</v>
       </c>
       <c r="W3" s="3">
         <v>3.290300000000002</v>
@@ -1220,13 +1220,13 @@
         </is>
       </c>
       <c r="AA3" s="3">
-        <v>60.52811431884766</v>
+        <v>60.528114</v>
       </c>
       <c r="AB3" s="3">
-        <v>54.04392242431641</v>
+        <v>54.043922</v>
       </c>
       <c r="AC3" s="3">
-        <v>41.54251098632812</v>
+        <v>41.54251</v>
       </c>
       <c r="AD3" s="3">
         <v>0</v>
@@ -1238,55 +1238,55 @@
         <v>0</v>
       </c>
       <c r="AG3" s="3">
-        <v>0.1817121505737305</v>
+        <v>0.18171215</v>
       </c>
       <c r="AH3" s="3">
-        <v>0.2259128093719482</v>
+        <v>0.22591281</v>
       </c>
       <c r="AI3" s="3">
-        <v>0.6951167583465576</v>
+        <v>0.69511676</v>
       </c>
       <c r="AJ3" s="3">
-        <v>0.09010275453329086</v>
+        <v>0.09010275500000001</v>
       </c>
       <c r="AK3" s="3">
-        <v>0.6656471490859985</v>
+        <v>0.66564715</v>
       </c>
       <c r="AL3" s="3">
-        <v>0.2871345579624176</v>
+        <v>0.28713456</v>
       </c>
       <c r="AM3" s="3">
-        <v>0.5867720246315002</v>
+        <v>0.586772</v>
       </c>
       <c r="AN3" s="3">
-        <v>0.5658631920814514</v>
+        <v>0.5658632</v>
       </c>
       <c r="AO3" s="3">
-        <v>0.09989241510629654</v>
+        <v>0.099892415</v>
       </c>
       <c r="AP3" s="3">
-        <v>0.7679430246353149</v>
+        <v>0.767943</v>
       </c>
       <c r="AQ3" s="3">
-        <v>0.9997621774673462</v>
+        <v>0.9997622</v>
       </c>
       <c r="AR3" s="3">
-        <v>0.7646519541740417</v>
+        <v>0.76465195</v>
       </c>
       <c r="AS3" s="3">
-        <v>0.967028021812439</v>
+        <v>0.967028</v>
       </c>
       <c r="AT3" s="3">
-        <v>0.6451165676116943</v>
+        <v>0.64511657</v>
       </c>
       <c r="AU3" s="3">
-        <v>-4.58236026763916</v>
+        <v>-4.5823603</v>
       </c>
       <c r="AV3" s="3">
-        <v>95.09494018554688</v>
+        <v>95.09493999999999</v>
       </c>
       <c r="AW3" s="3">
-        <v>8.92332649230957</v>
+        <v>8.9233265</v>
       </c>
       <c r="AX3" s="3">
         <v>353.4660000000002</v>
@@ -1301,7 +1301,7 @@
         <v>4</v>
       </c>
       <c r="BB3" s="3">
-        <v>3.459755637306095</v>
+        <v>3.459755637306096</v>
       </c>
       <c r="BC3" s="3">
         <v>0.7266938180771005</v>
@@ -1357,7 +1357,7 @@
         <v>1.071027324227294</v>
       </c>
       <c r="M4" s="3">
-        <v>0.453485570103045</v>
+        <v>0.4534855701030449</v>
       </c>
       <c r="N4" s="3">
         <v>17.84268628492911</v>
@@ -1369,13 +1369,13 @@
         <v>4.928972675772706</v>
       </c>
       <c r="Q4" s="3">
-        <v>0.453485570103045</v>
+        <v>0.4534855701030449</v>
       </c>
       <c r="R4" s="3">
         <v>1.521232540661306</v>
       </c>
       <c r="S4" s="3">
-        <v>91.17148772678067</v>
+        <v>91.17148772678068</v>
       </c>
       <c r="T4" s="3">
         <v>4.040140958370738</v>
@@ -1384,7 +1384,7 @@
         <v>5.817804393174674</v>
       </c>
       <c r="V4" s="3">
-        <v>0.453485570103045</v>
+        <v>0.4534855701030449</v>
       </c>
       <c r="W4" s="3">
         <v>2.681100000000002</v>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="AA4" s="3">
-        <v>16.76943588256836</v>
+        <v>16.769436</v>
       </c>
       <c r="AB4" s="3">
-        <v>33.80720520019531</v>
+        <v>33.807205</v>
       </c>
       <c r="AC4" s="3">
-        <v>41.89714431762695</v>
+        <v>41.897144</v>
       </c>
       <c r="AD4" s="3">
         <v>0</v>
@@ -1419,55 +1419,55 @@
         <v>0</v>
       </c>
       <c r="AG4" s="3">
-        <v>0.2616260647773743</v>
+        <v>0.26162606</v>
       </c>
       <c r="AH4" s="3">
-        <v>0.2681745886802673</v>
+        <v>0.2681746</v>
       </c>
       <c r="AI4" s="3">
-        <v>0.7960621118545532</v>
+        <v>0.7960621</v>
       </c>
       <c r="AJ4" s="3">
-        <v>0.07101662456989288</v>
+        <v>0.071016625</v>
       </c>
       <c r="AK4" s="3">
-        <v>0.6336730718612671</v>
+        <v>0.6336731</v>
       </c>
       <c r="AL4" s="3">
-        <v>0.07451099902391434</v>
+        <v>0.07451099999999999</v>
       </c>
       <c r="AM4" s="3">
-        <v>0.2241442948579788</v>
+        <v>0.2241443</v>
       </c>
       <c r="AN4" s="3">
-        <v>0.2897434830665588</v>
+        <v>0.28974348</v>
       </c>
       <c r="AO4" s="3">
-        <v>0.03194588422775269</v>
+        <v>0.031945884</v>
       </c>
       <c r="AP4" s="3">
-        <v>0.6579321026802063</v>
+        <v>0.6579321</v>
       </c>
       <c r="AQ4" s="3">
-        <v>0.9988958239555359</v>
+        <v>0.9988958</v>
       </c>
       <c r="AR4" s="3">
-        <v>0.8549615740776062</v>
+        <v>0.8549616</v>
       </c>
       <c r="AS4" s="3">
-        <v>0.8917741775512695</v>
+        <v>0.8917742</v>
       </c>
       <c r="AT4" s="3">
-        <v>0.5444017648696899</v>
+        <v>0.54440176</v>
       </c>
       <c r="AU4" s="3">
-        <v>-4.591850757598877</v>
+        <v>-4.5918508</v>
       </c>
       <c r="AV4" s="3">
-        <v>92.46042633056641</v>
+        <v>92.46043</v>
       </c>
       <c r="AW4" s="3">
-        <v>9.764013290405273</v>
+        <v>9.764013</v>
       </c>
       <c r="AX4" s="3">
         <v>389.4990000000001</v>
@@ -1582,13 +1582,13 @@
         </is>
       </c>
       <c r="AA5" s="3">
-        <v>60.20293426513672</v>
+        <v>60.202934</v>
       </c>
       <c r="AB5" s="3">
-        <v>61.03471755981445</v>
+        <v>61.034718</v>
       </c>
       <c r="AC5" s="3">
-        <v>46.73542022705078</v>
+        <v>46.73542</v>
       </c>
       <c r="AD5" s="3">
         <v>0</v>
@@ -1600,55 +1600,55 @@
         <v>0</v>
       </c>
       <c r="AG5" s="3">
-        <v>0.2031314820051193</v>
+        <v>0.20313148</v>
       </c>
       <c r="AH5" s="3">
-        <v>0.2511689364910126</v>
+        <v>0.25116894</v>
       </c>
       <c r="AI5" s="3">
-        <v>0.8450652360916138</v>
+        <v>0.8450652400000001</v>
       </c>
       <c r="AJ5" s="3">
-        <v>0.1027115136384964</v>
+        <v>0.10271151</v>
       </c>
       <c r="AK5" s="3">
-        <v>0.6776825189590454</v>
+        <v>0.6776825</v>
       </c>
       <c r="AL5" s="3">
-        <v>0.4971807599067688</v>
+        <v>0.49718076</v>
       </c>
       <c r="AM5" s="3">
-        <v>0.5462123155593872</v>
+        <v>0.5462123</v>
       </c>
       <c r="AN5" s="3">
-        <v>0.6626511216163635</v>
+        <v>0.6626511</v>
       </c>
       <c r="AO5" s="3">
-        <v>0.08121009171009064</v>
+        <v>0.08121009</v>
       </c>
       <c r="AP5" s="3">
-        <v>0.8647303581237793</v>
+        <v>0.86473036</v>
       </c>
       <c r="AQ5" s="3">
-        <v>0.9997215270996094</v>
+        <v>0.9997215</v>
       </c>
       <c r="AR5" s="3">
-        <v>0.8227964639663696</v>
+        <v>0.82279646</v>
       </c>
       <c r="AS5" s="3">
-        <v>0.9525008201599121</v>
+        <v>0.9525008</v>
       </c>
       <c r="AT5" s="3">
-        <v>0.6856838464736938</v>
+        <v>0.68568385</v>
       </c>
       <c r="AU5" s="3">
-        <v>-4.631178855895996</v>
+        <v>-4.631179</v>
       </c>
       <c r="AV5" s="3">
-        <v>98.99516296386719</v>
+        <v>98.99516</v>
       </c>
       <c r="AW5" s="3">
-        <v>5.876406669616699</v>
+        <v>5.8764067</v>
       </c>
       <c r="AX5" s="3">
         <v>373.4560000000001</v>
@@ -1725,7 +1725,7 @@
         <v>8.599463762035141</v>
       </c>
       <c r="O6" s="3">
-        <v>3.534988500955275</v>
+        <v>3.534988500955276</v>
       </c>
       <c r="P6" s="3">
         <v>5.104644142860336</v>
@@ -1763,13 +1763,13 @@
         </is>
       </c>
       <c r="AA6" s="3">
-        <v>45.21793365478516</v>
+        <v>45.217934</v>
       </c>
       <c r="AB6" s="3">
-        <v>49.32834625244141</v>
+        <v>49.328346</v>
       </c>
       <c r="AC6" s="3">
-        <v>40.18856048583984</v>
+        <v>40.18856</v>
       </c>
       <c r="AD6" s="3">
         <v>0</v>
@@ -1781,55 +1781,55 @@
         <v>0</v>
       </c>
       <c r="AG6" s="3">
-        <v>0.1176017299294472</v>
+        <v>0.11760173</v>
       </c>
       <c r="AH6" s="3">
-        <v>0.2769882082939148</v>
+        <v>0.2769882</v>
       </c>
       <c r="AI6" s="3">
-        <v>0.6194230318069458</v>
+        <v>0.61942303</v>
       </c>
       <c r="AJ6" s="3">
-        <v>0.04037143662571907</v>
+        <v>0.040371437</v>
       </c>
       <c r="AK6" s="3">
-        <v>0.6872637867927551</v>
+        <v>0.6872638</v>
       </c>
       <c r="AL6" s="3">
-        <v>0.06891923397779465</v>
+        <v>0.068919234</v>
       </c>
       <c r="AM6" s="3">
-        <v>0.2316244542598724</v>
+        <v>0.23162445</v>
       </c>
       <c r="AN6" s="3">
-        <v>0.24135622382164</v>
+        <v>0.24135622</v>
       </c>
       <c r="AO6" s="3">
-        <v>0.03940944373607635</v>
+        <v>0.039409444</v>
       </c>
       <c r="AP6" s="3">
-        <v>0.7943633794784546</v>
+        <v>0.7943634000000001</v>
       </c>
       <c r="AQ6" s="3">
-        <v>0.9999027252197266</v>
+        <v>0.9999027</v>
       </c>
       <c r="AR6" s="3">
-        <v>0.8274046778678894</v>
+        <v>0.8274047</v>
       </c>
       <c r="AS6" s="3">
-        <v>0.9617129564285278</v>
+        <v>0.96171296</v>
       </c>
       <c r="AT6" s="3">
-        <v>0.5726358294487</v>
+        <v>0.5726358</v>
       </c>
       <c r="AU6" s="3">
-        <v>-4.615780830383301</v>
+        <v>-4.615781</v>
       </c>
       <c r="AV6" s="3">
-        <v>93.75773620605469</v>
+        <v>93.75774</v>
       </c>
       <c r="AW6" s="3">
-        <v>10.07414436340332</v>
+        <v>10.074144</v>
       </c>
       <c r="AX6" s="3">
         <v>395.5470000000003</v>
@@ -1900,7 +1900,7 @@
         <v>1.219938036588334</v>
       </c>
       <c r="M7" s="3">
-        <v>0.3677264463853309</v>
+        <v>0.3677264463853308</v>
       </c>
       <c r="N7" s="3">
         <v>22.34409214041806</v>
@@ -1912,7 +1912,7 @@
         <v>4.780061963411666</v>
       </c>
       <c r="Q7" s="3">
-        <v>0.3677264463853309</v>
+        <v>0.3677264463853308</v>
       </c>
       <c r="R7" s="3">
         <v>3.156415749265656</v>
@@ -1927,7 +1927,7 @@
         <v>5.500805798326915</v>
       </c>
       <c r="V7" s="3">
-        <v>0.3677264463853309</v>
+        <v>0.3677264463853308</v>
       </c>
       <c r="W7" s="3">
         <v>3.080500000000002</v>
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="AA7" s="3">
-        <v>31.94557189941406</v>
+        <v>31.945572</v>
       </c>
       <c r="AB7" s="3">
-        <v>25.61627197265625</v>
+        <v>25.616272</v>
       </c>
       <c r="AC7" s="3">
-        <v>50.80400848388672</v>
+        <v>50.80401</v>
       </c>
       <c r="AD7" s="3">
         <v>0</v>
@@ -1962,55 +1962,55 @@
         <v>0</v>
       </c>
       <c r="AG7" s="3">
-        <v>0.1181811913847923</v>
+        <v>0.11818119</v>
       </c>
       <c r="AH7" s="3">
-        <v>0.2883137464523315</v>
+        <v>0.28831375</v>
       </c>
       <c r="AI7" s="3">
-        <v>0.8626953959465027</v>
+        <v>0.8626954</v>
       </c>
       <c r="AJ7" s="3">
-        <v>0.02938465401530266</v>
+        <v>0.029384654</v>
       </c>
       <c r="AK7" s="3">
-        <v>0.7931297421455383</v>
+        <v>0.79312974</v>
       </c>
       <c r="AL7" s="3">
-        <v>0.1443172991275787</v>
+        <v>0.1443173</v>
       </c>
       <c r="AM7" s="3">
-        <v>0.4411754012107849</v>
+        <v>0.4411754</v>
       </c>
       <c r="AN7" s="3">
-        <v>0.6368086934089661</v>
+        <v>0.6368087</v>
       </c>
       <c r="AO7" s="3">
-        <v>0.07752671092748642</v>
+        <v>0.07752671</v>
       </c>
       <c r="AP7" s="3">
-        <v>0.9581480026245117</v>
+        <v>0.958148</v>
       </c>
       <c r="AQ7" s="3">
-        <v>0.9999772310256958</v>
+        <v>0.9999772300000001</v>
       </c>
       <c r="AR7" s="3">
-        <v>0.7677334547042847</v>
+        <v>0.76773345</v>
       </c>
       <c r="AS7" s="3">
-        <v>0.9165694117546082</v>
+        <v>0.9165694</v>
       </c>
       <c r="AT7" s="3">
-        <v>0.5979740619659424</v>
+        <v>0.59797406</v>
       </c>
       <c r="AU7" s="3">
-        <v>-5.045364856719971</v>
+        <v>-5.045365</v>
       </c>
       <c r="AV7" s="3">
-        <v>96.46507263183594</v>
+        <v>96.46507</v>
       </c>
       <c r="AW7" s="3">
-        <v>7.68954610824585</v>
+        <v>7.689546</v>
       </c>
       <c r="AX7" s="3">
         <v>427.5080000000003</v>
